--- a/input/00_template_utilty_forecast_disagg.xlsx
+++ b/input/00_template_utilty_forecast_disagg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A40BAE9-408E-4C87-9B09-3ECE9DAD0D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{6A40BAE9-408E-4C87-9B09-3ECE9DAD0D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2812E824-ECBE-46F3-AD2E-7115A15A45D0}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{06CF607F-2E22-493E-8AF6-0597C12FB4D5}"/>
+    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{06CF607F-2E22-493E-8AF6-0597C12FB4D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sector_Forecast" sheetId="1" r:id="rId1"/>
@@ -2054,7 +2054,7 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.140625" customWidth="1"/>
@@ -2447,21 +2447,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B011C3FEFFEFCF44990405A8404263A2" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8dfd3bc83a02ed6a3437faf473449a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8a600ae29b0fcdec2bdff655f54bd0a0" ns2:_="">
     <xsd:import namespace="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
@@ -2605,10 +2590,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD0CBF33-FC10-41CD-93D1-F82E1691EAA8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F3F0F8-F9BE-4561-BE5A-23F21D2F14D5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2630,19 +2640,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F3F0F8-F9BE-4561-BE5A-23F21D2F14D5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD0CBF33-FC10-41CD-93D1-F82E1691EAA8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>